--- a/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.15485_1618870/10.15485_1618870_soil_Carbon__Dissolved_organic_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.15485_1618870/10.15485_1618870_soil_Carbon__Dissolved_organic_carbon.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,8 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +514,11 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>source_row</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -530,12 +536,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>El Verde:Ridge:a:1:2017-04-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -569,9 +575,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -588,12 +597,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>El Verde:Ridge:b:1:2017-04-01</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -627,9 +636,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -646,12 +658,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>El Verde:Ridge:c:1:2017-04-01</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -685,9 +697,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -704,12 +719,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>El Verde:Ridge:a:2:2017-04-01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -743,9 +758,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -762,12 +780,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>El Verde:Ridge:b:2:2017-04-01</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -801,9 +819,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -820,12 +841,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>El Verde:Ridge:c:2:2017-04-01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -859,9 +880,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -878,12 +902,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>El Verde:Ridge:a:3:2017-04-01</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -917,9 +941,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -936,12 +963,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>El Verde:Ridge:b:3:2017-04-01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -975,9 +1002,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -994,12 +1024,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>El Verde:Ridge:c:3:2017-04-01</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1033,9 +1063,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1085,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>El Verde:Slope:a:1:2017-04-01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1091,9 +1124,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1146,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>El Verde:Slope:b:1:2017-04-01</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1149,9 +1185,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1207,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>El Verde:Slope:c:1:2017-04-01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1207,9 +1246,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1268,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>El Verde:Slope:a:2:2017-04-01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1265,9 +1307,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1329,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>El Verde:Slope:b:2:2017-04-01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1323,9 +1368,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1390,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>El Verde:Slope:c:2:2017-04-01</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1381,9 +1429,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1451,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>El Verde:Slope:a:3:2017-04-01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1439,9 +1490,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1512,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>El Verde:Slope:b:3:2017-04-01</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1497,9 +1551,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1573,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>El Verde:Slope:c:3:2017-04-01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1555,9 +1612,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1634,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>El Verde:Slope:a:1:2017-04-01</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1613,9 +1673,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N20" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1695,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>El Verde:Slope:b:1:2017-04-01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1671,9 +1734,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N21" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1756,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>El Verde:Slope:c:1:2017-04-01</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1729,9 +1795,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N22" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1817,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>El Verde:Slope:a:2:2017-04-01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1787,9 +1856,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1878,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>El Verde:Slope:b:2:2017-04-01</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1845,9 +1917,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1939,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>El Verde:Slope:c:2:2017-04-01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1903,9 +1978,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N25" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1922,12 +2000,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>El Verde:Slope:a:3:2017-04-01</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1961,9 +2039,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -1980,12 +2061,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>El Verde:Slope:b:3:2017-04-01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2019,9 +2100,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N27" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2122,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>El Verde:Slope:c:3:2017-04-01</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2077,9 +2161,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N28" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2183,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>El Verde:Valley:a:1:2017-04-01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2135,9 +2222,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2244,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>El Verde:Valley:b:1:2017-04-01</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2193,9 +2283,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N30" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2305,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>El Verde:Valley:c:1:2017-04-01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2251,9 +2344,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N31" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2366,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>El Verde:Valley:a:2:2017-04-01</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2309,9 +2405,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N32" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2427,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>El Verde:Valley:b:2:2017-04-01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2367,9 +2466,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N33" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2488,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>El Verde:Valley:c:2:2017-04-01</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2425,9 +2527,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2549,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>El Verde:Valley:a:3:2017-04-01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2483,9 +2588,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N35" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2610,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>El Verde:Valley:b:3:2017-04-01</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2541,9 +2649,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N36" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2671,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>El Verde:Valley:c:3:2017-04-01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2599,9 +2710,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N37" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2732,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>El Verde:Ridge:a:1:2017-08-01</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2657,9 +2771,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N38" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2793,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>El Verde:Ridge:b:1:2017-08-01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2715,9 +2832,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N39" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2854,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>El Verde:Ridge:a:2:2017-08-01</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2773,9 +2893,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N40" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2915,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>El Verde:Ridge:b:2:2017-08-01</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2831,9 +2954,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N41" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2976,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>El Verde:Ridge:a:3:2017-08-01</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2889,9 +3015,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N42" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2908,12 +3037,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>El Verde:Ridge:b:3:2017-08-01</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2947,9 +3076,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -2966,12 +3098,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>El Verde:Valley:a:1:2017-08-01</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -3005,9 +3137,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N44" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3159,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>El Verde:Valley:b:1:2017-08-01</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -3063,9 +3198,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N45" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3220,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>El Verde:Valley:a:2:2017-08-01</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -3121,9 +3259,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N46" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3281,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>El Verde:Valley:b:2:2017-08-01</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -3179,9 +3320,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N47" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3342,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>El Verde:Valley:a:3:2017-08-01</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -3237,9 +3381,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N48" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3403,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>El Verde:Valley:b:3:2017-08-01</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -3295,9 +3442,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N49" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3464,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>El Verde:Ridge:a:1:NA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3349,9 +3499,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N50" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3521,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>El Verde:Ridge:b:1:NA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3403,9 +3556,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N51" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3578,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>El Verde:Ridge:a:2:NA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -3457,9 +3613,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N52" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3635,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>El Verde:Ridge:b:2:NA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3511,9 +3670,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N53" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3692,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>El Verde:Ridge:a:3:NA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3565,9 +3727,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N54" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3749,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>El Verde:Ridge:b:3:NA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3619,9 +3784,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N55" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3806,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>El Verde:Slope:a:1:NA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3673,9 +3841,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N56" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3863,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>El Verde:Slope:b:1:NA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3727,9 +3898,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N57" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3920,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>El Verde:Slope:a:2:NA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3781,9 +3955,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N58" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3977,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>El Verde:Slope:b:2:NA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3835,9 +4012,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N59" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3854,12 +4034,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>El Verde:Slope:a:3:NA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3889,9 +4069,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N60" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3908,12 +4091,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>El Verde:Slope:b:3:NA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3943,9 +4126,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N61" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -3962,12 +4148,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>El Verde:Valley:a:1:NA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3997,9 +4183,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N62" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4205,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>El Verde:Valley:b:1:NA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -4051,9 +4240,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N63" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4262,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>El Verde:Valley:a:2:NA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -4105,9 +4297,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N64" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4319,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>El Verde:Valley:b:2:NA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -4159,9 +4354,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N65" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4376,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>El Verde:Valley:a:3:NA</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -4213,9 +4411,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N66" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4433,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>El Verde:Valley:b:3:NA</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -4267,9 +4468,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N67" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4490,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>El Verde:Ridge:a:1:2018-01-01</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -4325,9 +4529,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N68" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4551,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>El Verde:Ridge:b:1:2018-01-01</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -4383,9 +4590,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N69" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4612,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>El Verde:Slope:a:1:2018-01-01</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4441,9 +4651,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N70" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4460,12 +4673,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>El Verde:Slope:b:1:2018-01-01</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4499,9 +4712,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N71" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4734,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>El Verde:Slope:a:1:2018-01-01</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4557,9 +4773,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N72" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4795,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>El Verde:Slope:b:1:2018-01-01</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4615,9 +4834,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N73" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4856,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>El Verde:Valley:a:1:2018-01-01</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4673,9 +4895,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N74" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4917,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>El Verde:Valley:b:1:2018-01-01</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4731,9 +4956,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N75" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4750,12 +4978,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>El Verde:Ridge:a:1:2018-05-01</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4789,9 +5017,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N76" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4808,12 +5039,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>El Verde:Ridge:b:1:2018-05-01</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4847,9 +5078,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N77" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4866,12 +5100,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>El Verde:Ridge:c:1:2018-05-01</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4905,9 +5139,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N78" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4924,12 +5161,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>El Verde:Valley:a:1:2018-05-01</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4963,9 +5200,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N79" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -4982,12 +5222,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>El Verde:Valley:b:1:2018-05-01</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -5021,9 +5261,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N80" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5283,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>El Verde:Valley:c:1:2018-05-01</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>source_row</t>
+          <t>Soil Site:Topographic_locations:Lab_replicate:Field_replicate:date</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -5079,9 +5322,12 @@
         <v>-65.81948</v>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); several methods described in the package</t>
+      <c r="N81" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.15485/1618870 package spatialCoverage point; source column DOC_mg_g (mg/g, unit from column name); converted from mg/g to mg C kg-1 dry soil (x 1000); id not unique: 22 rows share an id; several methods described in the package</t>
         </is>
       </c>
     </row>
